--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/12 05:48:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>我也想忘</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/12 05:48:26</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1250</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2500</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/12 05:49:26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2500</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2500</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2475</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
+          <t>06/12 05:52:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>我也想忘</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/12 05:48:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>我也想忘</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/12 05:48:26</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/12 05:49:26</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>22000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2794.55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2475</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2769.55</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -75,17 +75,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:52:03</t>
+          <t>06/12 05:52:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>1413.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
+          <t>06/12 05:52:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>我也想忘</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,210 +159,252 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/12 05:48:52</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>我也想忘</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/12 05:48:26</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/12 05:49:26</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>22000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2794.55</t>
+          <t>32000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4208.39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2769.55</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4183.39</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -75,27 +75,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/12 05:52:18</t>
+          <t>06/12 14:43:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1413.84</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,129 +114,53 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/12 05:52:03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6.79</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>294.55</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/12 05:48:52</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>我也想忘</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/12 05:48:26</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -244,7 +168,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
@@ -261,30 +185,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -294,117 +203,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/12 05:49:26</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>11.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>32000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4208.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4183.39</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11.11</t>
         </is>
       </c>
     </row>

--- a/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
+++ b/bills/6897265765/1a4f672201624a3b0612098300684f77d8436cfeec5a9701d81f2da8464c2fa9/bill-2026-06-12.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/12 15:37:24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>37889</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4209.89</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/12 14:43:39</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>37989</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4221</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11.11</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4221</t>
         </is>
       </c>
     </row>
